--- a/stories/arbres/ATOM-JEU.FOOT.001-05.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kilian et papa sont au jardin. Papa pose deux seaux. C'est le but. Il pose une corde. Papa dit : voici l'espace montré. On reste dans l'espace montré. Kilian touche le ballon du pied. Papa dit : on va passer le ballon. Puis on vise le but. Kilian passe le ballon. Papa le rend. Kilian pousse le ballon vers le but. Le ballon roule entre les seaux. Les pieds restent dans l'espace montré par papa. Plus tard, le ballon va près de la corde. Kilian se souvient. Il revient dans l'espace montré. Il passe encore. Il vise encore le but. Même leçon, autre essai.</t>
+          <t>Kilian et papa sont au jardin. Papa pose deux seaux. C'est le but. Il pose une corde. Voici l'espace montré. On reste dans l'espace montré. Kilian touche le ballon du pied. On va passer le ballon. Puis on vise le but. Kilian passe le ballon. Papa le rend. Kilian pousse le ballon vers le but. Le ballon roule entre les seaux. Les pieds restent dans l'espace montré par papa. Plus tard, le ballon va près de la corde. Kilian se souvient. Il revient dans l'espace montré. Il passe encore. Il vise encore le but. Même leçon, autre essai.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kilian et papa sont au jardin. Papa pose deux seaux. C'est le but. Il pose une corde.
+papa|Voici l'espace montré. On reste dans l'espace montré.
+narrateur|Kilian touche le ballon du pied.
+papa|On va passer le ballon.
+narrateur|Puis on vise le but. Kilian passe le ballon. Papa le rend. Kilian pousse le ballon vers le but. Le ballon roule entre les seaux. Les pieds restent dans l'espace montré par papa. Plus tard, le ballon va près de la corde. Kilian se souvient. Il revient dans l'espace montré. Il passe encore. Il vise encore le but. Même leçon, autre essai.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Kilian joue au foot. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kilian a passé le ballon. Il a visé le but. Il est resté dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range les seaux. Kilian boit une gorgée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-05.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Puis on vise le but. Kilian passe le ballon. Papa le rend. Kilian pousse le ballon vers le but. Le ballon roule entre les seaux. Les pieds restent dans l'espace montré par papa. Plus tard, le ballon va près de la corde. Kilian se souvient. Il revient dans l'espace montré. Il passe encore. Il vise encore le but. Même leçon, autre essai.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Kilian joue au foot. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Kilian a passé le ballon. Il a visé le but. Il est resté dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Papa range les seaux. Kilian boit une gorgée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.FOOT.001-05.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kilian vise le but au jardin</t>
+          <t>La chaussette sous le fil</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JEU.REG.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une chaussette rayée attend sous le fil. Aniss se passe le ballon avec papa. Il vise le but. Quand le ballon va près de la corde, il revient dans l'espace montré.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kilian et papa sont au jardin. Papa pose deux seaux. C'est le but. Il pose une corde. Voici l'espace montré. On reste dans l'espace montré. Kilian touche le ballon du pied. On va passer le ballon. Puis on vise le but. Kilian passe le ballon. Papa le rend. Kilian pousse le ballon vers le but. Le ballon roule entre les seaux. Les pieds restent dans l'espace montré par papa. Plus tard, le ballon va près de la corde. Kilian se souvient. Il revient dans l'espace montré. Il passe encore. Il vise encore le but. Même leçon, autre essai.</t>
+          <t>Une chaussette rayée est tombée sous le fil. Les fourmis font la file sur une pierre. Ça sent l'herbe coupée. Un linge blanc bouge un peu. Une pince à linge est tombée. Elle est bleue. Tu la vois, Aniss ? Elle est sous le fil. On la pose près de la chaussette. Papa pose la pince sur le rebord. Un papillon blanc passe. Il est tout léger. Oui. Il va où il veut. Tu as vu la chaussette, Aniss ? Elle est sous le fil. Elle est un peu sèche. Papa la pose sur le rebord. Merci. On la range après. En ce moment, Aniss est au jardin. Papa pose deux seaux. C'est le but. Il pose une corde. Voici l'espace montré. On reste dans l'espace montré. Aniss touche le ballon du pied. Il est souple. Il sent l'herbe. On va passer le ballon. Puis on vise le but. Aniss passe le ballon. Papa le rend. Bravo. Tu as passé. Aniss pousse le ballon vers le but. Le ballon roule entre les seaux. Les pieds restent dans l'espace montré. Dedans ! Bravo, Aniss. Tu as visé le but. Plus tard, le ballon va près de la corde. Aniss s'arrête. Il se souvient. Il revient dans l'espace montré. Bravo. On reste dans l'espace montré. Il passe encore. Papa rend. Il vise encore le but. Le ballon roule entre les seaux. Les fourmis sont encore sur la pierre. Un dernier passage ? Oui, papa. Aniss passe. Papa rend. Aniss pousse vers le but. Dans l'espace montré. Bravo. Tu as passé. Tu as visé le but. On a rejoué dans l'espace montré.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,75 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kilian et papa sont au jardin. Papa pose deux seaux. C'est le but. Il pose une corde.
-papa|Voici l'espace montré. On reste dans l'espace montré.
-narrateur|Kilian touche le ballon du pied.
+          <t>narrateur|Une chaussette rayée est tombée sous le fil.
+narrateur|Les fourmis font la file sur une pierre.
+narrateur|Ça sent l'herbe coupée.
+narrateur|Un linge blanc bouge un peu.
+narrateur|Une pince à linge est tombée.
+narrateur|Elle est bleue.
+papa|Tu la vois, Aniss ?
+enfant-m|Elle est sous le fil.
+papa|On la pose près de la chaussette.
+narrateur|Papa pose la pince sur le rebord.
+narrateur|Un papillon blanc passe.
+enfant-m|Il est tout léger.
+papa|Oui.
+papa|Il va où il veut.
+papa|Tu as vu la chaussette, Aniss ?
+enfant-m|Elle est sous le fil.
+enfant-m|Elle est un peu sèche.
+narrateur|Papa la pose sur le rebord.
+enfant-m|Merci.
+papa|On la range après.
+narrateur|En ce moment, Aniss est au jardin.
+narrateur|Papa pose deux seaux.
+narrateur|C'est le but.
+narrateur|Il pose une corde.
+papa|Voici l'espace montré.
+papa|On reste dans l'espace montré.
+narrateur|Aniss touche le ballon du pied.
+narrateur|Il est souple.
+enfant-m|Il sent l'herbe.
 papa|On va passer le ballon.
-narrateur|Puis on vise le but. Kilian passe le ballon. Papa le rend. Kilian pousse le ballon vers le but. Le ballon roule entre les seaux. Les pieds restent dans l'espace montré par papa. Plus tard, le ballon va près de la corde. Kilian se souvient. Il revient dans l'espace montré. Il passe encore. Il vise encore le but. Même leçon, autre essai.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Puis on vise le but.
+narrateur|Aniss passe le ballon.
+narrateur|Papa le rend.
+papa|Bravo.
+papa|Tu as passé.
+narrateur|Aniss pousse le ballon vers le but.
+narrateur|Le ballon roule entre les seaux.
+narrateur|Les pieds restent dans l'espace montré.
+enfant-m|Dedans !
+papa|Bravo, Aniss.
+papa|Tu as visé le but.
+narrateur|Plus tard, le ballon va près de la corde.
+narrateur|Aniss s'arrête.
+narrateur|Il se souvient.
+narrateur|Il revient dans l'espace montré.
+papa|Bravo.
+papa|On reste dans l'espace montré.
+narrateur|Il passe encore.
+narrateur|Papa rend.
+narrateur|Il vise encore le but.
+narrateur|Le ballon roule entre les seaux.
+narrateur|Les fourmis sont encore sur la pierre.
+papa|Un dernier passage ?
+enfant-m|Oui, papa.
+narrateur|Aniss passe.
+narrateur|Papa rend.
+narrateur|Aniss pousse vers le but.
+narrateur|Dans l'espace montré.
+papa|Bravo.
+papa|Tu as passé.
+papa|Tu as visé le but.
+papa|On a rejoué dans l'espace montré.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>linge,ballon</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1422,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Kilian joue au foot. Que fait-il ?</t>
+          <t>Aniss joue au foot. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1578,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Kilian joue au foot. Que fait-il ?</t>
+          <t>narrateur|Aniss joue au foot.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kilian a passé le ballon. Il a visé le but. Il est resté dans l'espace montré.</t>
+          <t>Aniss a passé le ballon. Il a visé le but. Il est resté dans l'espace montré. Tu as passé, Aniss. Bravo. Tu as visé le but. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1751,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kilian a passé le ballon. Il a visé le but. Il est resté dans l'espace montré.</t>
+          <t>narrateur|Aniss a passé le ballon.
+narrateur|Il a visé le but.
+narrateur|Il est resté dans l'espace montré.
+papa|Tu as passé, Aniss.
+papa|Bravo.
+papa|Tu as visé le but.
+enfant-m|Dans l'espace montré.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range les seaux. Kilian boit une gorgée.</t>
+          <t>Papa range les seaux. Aniss boit une gorgée. La chaussette rayée est sur le rebord. Tu la prends ? Aniss la prend. Elle est sèche. Tu as visé le but. Oui, papa. J'ai passé. Dans l'espace montré. Bravo. Tu as fait du bon travail. Les fourmis sont encore sur la pierre. Le linge blanc bouge un peu. Ils marchent vers la maison. Aniss tient la chaussette. Papa tient la pince bleue. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Tu es revenu dans l'espace montré. Oui, papa. Le linge blanc bouge encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,10 +1921,37 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range les seaux. Kilian boit une gorgée.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa range les seaux.
+narrateur|Aniss boit une gorgée.
+narrateur|La chaussette rayée est sur le rebord.
+papa|Tu la prends ?
+narrateur|Aniss la prend.
+enfant-m|Elle est sèche.
+papa|Tu as visé le but.
+enfant-m|Oui, papa.
+enfant-m|J'ai passé.
+enfant-m|Dans l'espace montré.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Les fourmis sont encore sur la pierre.
+narrateur|Le linge blanc bouge un peu.
+narrateur|Ils marchent vers la maison.
+narrateur|Aniss tient la chaussette.
+narrateur|Papa tient la pince bleue.
+papa|Tu as passé.
+papa|Tu as visé le but.
+enfant-m|Dans l'espace montré.
+papa|C'est ça.
+papa|Tu es revenu dans l'espace montré.
+enfant-m|Oui, papa.
+narrateur|Le linge blanc bouge encore.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>linge,pas</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,7 +1976,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La chaussette rayée rentre à la maison. J'ai passé. J'ai visé le but. Bravo, Aniss. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2116,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La chaussette rayée rentre à la maison.
+enfant-m|J'ai passé.
+enfant-m|J'ai visé le but.
+papa|Bravo, Aniss.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2180,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-05.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-05.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kilian et papa sont au jardin. Papa pose deux seaux. C'est le &lt;emphasis level="moderate"&gt;but&lt;/emphasis&gt;. Il pose une corde. Papa dit : voici l'espace montré. On reste dans l'espace montré. Kilian touche le ballon du pied. Papa dit : on va passer le ballon. Puis on vise le but. Kilian passe le ballon. Papa le rend. Kilian pousse le ballon vers le but. Le ballon roule entre les seaux. Les pieds restent dans l'espace montré par papa. Plus tard, le ballon va près de la corde. Kilian se souvient. Il revient dans l'espace montré. Il passe encore. Il vise encore le but. Même leçon, autre essai.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une chaussette rayée est tombée sous le fil. Les fourmis font la file sur une pierre. Ça sent l'herbe coupée. Un linge blanc bouge un peu. Une pince à linge est tombée. Elle est bleue. Tu la vois, Aniss ? Elle est sous le fil. On la pose près de la chaussette. Papa pose la pince sur le rebord. Un papillon blanc passe. Il est tout léger. Oui. Il va où il veut. Tu as vu la chaussette, Aniss ? Elle est sous le fil. Elle est un peu sèche. Papa la pose sur le rebord. Merci. On la range après. En ce moment, Aniss est au jardin. Papa pose deux seaux. C'est le but. Il pose une corde. Voici l'espace montré. On reste dans l'espace montré. Aniss touche le ballon du pied. Il est souple. Il sent l'herbe. On va passer le ballon. Puis on vise le but. Aniss passe le ballon. Papa le rend. Bravo. Tu as passé. Aniss pousse le ballon vers le but. Le ballon roule entre les seaux. Les pieds restent dans l'espace montré. Dedans ! Bravo, Aniss. Tu as visé le but. Plus tard, le ballon va près de la corde. Aniss s'arrête. Il se souvient. Il revient dans l'espace montré. Bravo. On reste dans l'espace montré. Il passe encore. Papa rend. Il vise encore le but. Le ballon roule entre les seaux. Les fourmis sont encore sur la pierre. Un dernier passage ? Oui, papa. Aniss passe. Papa rend. Aniss pousse vers le but. Dans l'espace montré. Bravo. Tu as passé. Tu as visé le but. On a rejoué dans l'espace montré.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kilian joue au foot. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss joue au foot. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1582,7 +1582,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1612,7 +1611,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kilian a passé le ballon. Il a visé le &lt;emphasis level="moderate"&gt;but&lt;/emphasis&gt;. Il est resté dans l'espace montré.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a passé le ballon. Il a visé le but. Il est resté dans l'espace montré. Tu as passé, Aniss. Bravo. Tu as visé le but. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1760,7 +1759,6 @@
 enfant-m|Dans l'espace montré.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,12 +1783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range les seaux. Aniss boit une gorgée. La chaussette rayée est sur le rebord. Tu la prends ? Aniss la prend. Elle est sèche. Tu as visé le but. Oui, papa. J'ai passé. Dans l'espace montré. Bravo. Tu as fait du bon travail. Les fourmis sont encore sur la pierre. Le linge blanc bouge un peu. Ils marchent vers la maison. Aniss tient la chaussette. Papa tient la pince bleue. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Tu es revenu dans l'espace montré. Oui, papa. Le linge blanc bouge encore.</t>
+          <t>Papa range les seaux. Aniss boit une gorgée. La chaussette rayée est sur le rebord. Tu la prends ? Aniss la prend. Elle est sèche. Tu as visé le but. Oui, papa. J'ai passé. Dans l'espace montré. Bravo. Les fourmis sont encore sur la pierre. Le linge blanc bouge un peu. Ils marchent vers la maison. Aniss tient la chaussette. Papa tient la pince bleue. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Tu es revenu dans l'espace montré. Oui, papa. Le linge blanc bouge encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range les seaux. Kilian boit une gorgée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range les seaux. Aniss boit une gorgée. La chaussette rayée est sur le rebord. Tu la prends ? Aniss la prend. Elle est sèche. Tu as visé le but. Oui, papa. J'ai passé. Dans l'espace montré. Bravo. Les fourmis sont encore sur la pierre. Le linge blanc bouge un peu. Ils marchent vers la maison. Aniss tient la chaussette. Papa tient la pince bleue. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Tu es revenu dans l'espace montré. Oui, papa. Le linge blanc bouge encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1932,7 +1930,6 @@
 enfant-m|J'ai passé.
 enfant-m|Dans l'espace montré.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Les fourmis sont encore sur la pierre.
 narrateur|Le linge blanc bouge un peu.
 narrateur|Ils marchent vers la maison.
@@ -1976,12 +1973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La chaussette rayée rentre à la maison. J'ai passé. J'ai visé le but. Bravo, Aniss. L'histoire est finie.</t>
+          <t>La chaussette rayée rentre à la maison. J'ai passé. J'ai visé le but. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La chaussette rayée rentre à la maison. J'ai passé. J'ai visé le but. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2119,11 +2116,9 @@
           <t>narrateur|La chaussette rayée rentre à la maison.
 enfant-m|J'ai passé.
 enfant-m|J'ai visé le but.
-papa|Bravo, Aniss.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Aniss.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2142,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2187,6 +2182,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-05.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-05.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kilian, papa</t>
+          <t>Aniss, papa</t>
         </is>
       </c>
     </row>
